--- a/Assets/Data/DataTable/05_QTE_Table.xlsx
+++ b/Assets/Data/DataTable/05_QTE_Table.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\github\Astrocat-2DSFProject\Assets\Data\DataTable\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB59D763-890E-40EA-AC08-6480D96C1737}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E954FD6-6D3A-41F1-942E-11EFA7D3DD86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1380" yWindow="2415" windowWidth="21600" windowHeight="11295" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="!Logic" sheetId="2" r:id="rId1"/>
     <sheet name="!Desc" sheetId="1" r:id="rId2"/>
-    <sheet name="!QTE" sheetId="3" r:id="rId3"/>
+    <sheet name="QTETable" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>

--- a/Assets/Data/DataTable/05_QTE_Table.xlsx
+++ b/Assets/Data/DataTable/05_QTE_Table.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\github\Astrocat-2DSFProject\Assets\Data\DataTable\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E954FD6-6D3A-41F1-942E-11EFA7D3DD86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C77DE7B-52B4-4B7F-A9FE-B35849B482D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="43095" yWindow="0" windowWidth="14610" windowHeight="7845" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="!Logic" sheetId="2" r:id="rId1"/>
@@ -400,7 +400,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="109">
   <si>
     <t>Hero_ID</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -814,6 +814,10 @@
   </si>
   <si>
     <t>enum:QTE_Type:NONE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>QTE_ID</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -4219,16 +4223,16 @@
     </row>
     <row r="3" spans="1:447" s="27" customFormat="1" ht="13.5" x14ac:dyDescent="0.3">
       <c r="A3" s="28" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="B3" s="29" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="C3" s="29" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="D3" s="29" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="E3" s="29" t="s">
         <v>106</v>
@@ -4696,7 +4700,7 @@
     </row>
     <row r="4" spans="1:447" s="27" customFormat="1" ht="13.5" x14ac:dyDescent="0.3">
       <c r="A4" s="26" t="s">
-        <v>55</v>
+        <v>108</v>
       </c>
       <c r="B4" s="26" t="s">
         <v>59</v>

--- a/Assets/Data/DataTable/05_QTE_Table.xlsx
+++ b/Assets/Data/DataTable/05_QTE_Table.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\github\Astrocat-2DSFProject\Assets\Data\DataTable\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C77DE7B-52B4-4B7F-A9FE-B35849B482D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9C8F3B4-3398-4F7B-B8DA-ED9971FEF631}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="43095" yWindow="0" windowWidth="14610" windowHeight="7845" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="!Logic" sheetId="2" r:id="rId1"/>
